--- a/ValueSet-skintone-vs.xlsx
+++ b/ValueSet-skintone-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-skintone-vs.xlsx
+++ b/ValueSet-skintone-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-skintone-vs.xlsx
+++ b/ValueSet-skintone-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-skintone-vs.xlsx
+++ b/ValueSet-skintone-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-skintone-vs.xlsx
+++ b/ValueSet-skintone-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-skintone-vs.xlsx
+++ b/ValueSet-skintone-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
